--- a/Dataset/IT/xlsx/ITAMed_2023.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2023.xlsx
@@ -829,7 +829,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Genetica Medica; Oncologia</t>
+          <t>Oncologia; Genetica Medica</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Oftalmologia; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Oftalmologia</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Chirurgia Generale; Oncologia</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Endocrinologia; Genetica Medica</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Chirurgia Generale</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Endocrinologia</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia; Pediatria</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Pediatria; Malattie Infettive</t>
+          <t>Malattie Infettive; Pediatria</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Dermatologia e Venereologia; Farmacologia e Tossicologia</t>
+          <t>Farmacologia e Tossicologia; Dermatologia e Venereologia</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Endocrinologia; Oncologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Psichiatria; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Psichiatria</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Farmacologia e Tossicologia</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Malattie Infettive</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Anestesia e Rianimazione</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Farmacologia e Tossicologia</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Oncologia; Ematologia</t>
+          <t>Ematologia</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Psichiatria</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Oncologia</t>
+          <t>Gastroenterologia; Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Oncologia</t>
+          <t>Ginecologia e Ostetricia; Chirurgia Generale</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Neurologia e Neurochirurgia</t>
+          <t>Malattie Infettive</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Genetica Medica; Pediatria</t>
+          <t>Pediatria; Malattie Infettive</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Medicina Legale</t>
+          <t>Igiene, Epidemiologia e Statistica; Medicina Legale</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Medicina Legale; Pediatria</t>
+          <t>Medicina Legale</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Immunologia e Reumatologia</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Urologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Farmacologia e Tossicologia</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Pneumologia e Chirurgia Toracica</t>
+          <t>Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">

--- a/Dataset/IT/xlsx/ITAMed_2023.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2023.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Immagine</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8716,7 +8716,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>

--- a/Dataset/IT/xlsx/ITAMed_2023.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2023.xlsx
@@ -4485,7 +4485,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endoscopic image </t>
+          <t>Endoscopic image</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">

--- a/Dataset/IT/xlsx/ITAMed_2023.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2023.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" bestFit="1" customWidth="1" min="13" max="13"/>
@@ -476,15 +476,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>Tipo Domanda</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Immagine</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Categoria Immagine</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Percorso Immagine</t>
         </is>
@@ -547,6 +552,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -605,6 +615,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -663,6 +678,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -721,6 +741,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -779,6 +804,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -837,6 +867,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -895,6 +930,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -953,6 +993,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1011,6 +1056,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1069,6 +1119,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1127,6 +1182,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1185,6 +1245,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1243,6 +1308,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1301,6 +1371,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1359,6 +1434,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1417,6 +1497,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1472,7 +1557,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1533,6 +1623,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1591,6 +1686,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1651,10 +1751,15 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>Radiological image</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>images/2023/ssm2023460.png</t>
         </is>
@@ -1719,10 +1824,15 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>Radiological image</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>images/2023/ssm2023461.png</t>
         </is>
@@ -1785,6 +1895,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1843,6 +1958,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1901,6 +2021,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1959,6 +2084,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2017,6 +2147,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2075,6 +2210,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2133,6 +2273,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2191,6 +2336,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2249,6 +2399,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2307,6 +2462,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2365,6 +2525,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2423,6 +2588,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2481,6 +2651,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2539,6 +2714,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2597,6 +2777,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2655,6 +2840,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2713,6 +2903,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2771,6 +2966,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2829,6 +3029,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2887,6 +3092,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2945,6 +3155,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3003,6 +3218,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3061,6 +3281,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3119,6 +3344,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3177,6 +3407,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3235,6 +3470,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3293,6 +3533,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3351,6 +3596,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3411,10 +3661,15 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>images/2023/ssm2023490.png</t>
         </is>
@@ -3479,10 +3734,15 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>images/2023/ssm2023491.png</t>
         </is>
@@ -3547,10 +3807,15 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>Peripheral blood smear</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>images/2023/ssm2023492.png</t>
         </is>
@@ -3613,6 +3878,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3671,6 +3941,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3729,6 +4004,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3787,6 +4067,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3845,6 +4130,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3903,6 +4193,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3961,6 +4256,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4019,6 +4319,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4077,6 +4382,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4135,6 +4445,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4193,6 +4508,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4251,6 +4571,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4309,6 +4634,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4367,6 +4697,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4425,6 +4760,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4485,10 +4825,15 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
           <t>Endoscopic image</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>images/2023/ssm2023508.png</t>
         </is>
@@ -4551,6 +4896,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4609,6 +4959,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4667,6 +5022,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4725,6 +5085,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4783,6 +5148,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4841,6 +5211,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4899,6 +5274,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4957,6 +5337,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5015,6 +5400,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5073,6 +5463,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5133,10 +5528,15 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>images/2023/ssm2023519.png</t>
         </is>
@@ -5199,6 +5599,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5257,6 +5662,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5315,6 +5725,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5373,6 +5788,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5431,6 +5851,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5489,6 +5914,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5547,6 +5977,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5605,6 +6040,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5663,6 +6103,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5721,6 +6166,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5779,6 +6229,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5837,6 +6292,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5895,6 +6355,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5953,6 +6418,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6011,6 +6481,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6069,6 +6544,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6127,6 +6607,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6185,6 +6670,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6243,6 +6733,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6301,6 +6796,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6359,6 +6859,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6417,6 +6922,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6475,6 +6985,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6533,6 +7048,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6591,6 +7111,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6649,6 +7174,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6709,10 +7239,15 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
           <t>Radiological image</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr">
+      <c r="O107" t="inlineStr">
         <is>
           <t>images/2023/ssm2023546.png</t>
         </is>
@@ -6775,6 +7310,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6835,10 +7375,15 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
           <t>Radiological image</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr">
+      <c r="O109" t="inlineStr">
         <is>
           <t>images/2023/ssm2023548.png</t>
         </is>
@@ -6903,10 +7448,15 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
           <t>Radiological image</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr">
+      <c r="O110" t="inlineStr">
         <is>
           <t>images/2023/ssm2023549.png</t>
         </is>
@@ -6969,6 +7519,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7027,6 +7582,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7085,6 +7645,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7143,6 +7708,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7201,6 +7771,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7259,6 +7834,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7317,6 +7897,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7375,6 +7960,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7433,6 +8023,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7491,6 +8086,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7549,6 +8149,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7607,6 +8212,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7665,6 +8275,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7723,6 +8338,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7781,6 +8401,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7839,6 +8464,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7897,6 +8527,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7955,6 +8590,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -8013,6 +8653,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8071,6 +8716,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8129,6 +8779,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8187,6 +8842,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8247,10 +8907,15 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr">
+      <c r="O133" t="inlineStr">
         <is>
           <t>images/2023/ssm2023572.png</t>
         </is>
@@ -8313,6 +8978,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8371,6 +9041,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8429,6 +9104,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8487,6 +9167,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8545,6 +9230,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8603,6 +9293,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8661,6 +9356,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8717,6 +9417,11 @@
       <c r="L141" t="inlineStr">
         <is>
           <t>case-based</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
